--- a/specs/001-fltiq-62-public-landing-page/test-cases.xlsx
+++ b/specs/001-fltiq-62-public-landing-page/test-cases.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-21T16:30:00</t>
+          <t>2026-09-21T20:45:00</t>
         </is>
       </c>
     </row>
@@ -795,10 +795,14 @@
       </c>
       <c r="M2" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N2" s="4" t="inlineStr"/>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="N2" s="4" t="inlineStr">
+        <is>
+          <t>automation/tests/ui/test_landing.py::test_tc001_unauthenticated_visitor_sees_landing_page</t>
+        </is>
+      </c>
       <c r="O2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
@@ -866,10 +870,14 @@
       </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr"/>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>automation/tests/ui/test_landing.py::test_tc002_header_create_account_navigates_to_signup</t>
+        </is>
+      </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
           <t>If FLTIQ-33 is not yet deployed to the target environment, verify at the routing/target-URL level only (spec.md §10) and skip the destination-page assertion with an explicit reason</t>
@@ -941,10 +949,14 @@
       </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr"/>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>automation/tests/ui/test_landing.py::test_tc003_hero_create_account_navigates_to_signup</t>
+        </is>
+      </c>
       <c r="O4" s="4" t="inlineStr">
         <is>
           <t>Same routing caveat as TC-002. Verified independently of the header instance per TR-004.</t>
@@ -1016,10 +1028,14 @@
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="inlineStr"/>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>automation/tests/ui/test_landing.py::test_tc004_closing_create_account_navigates_to_signup</t>
+        </is>
+      </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
           <t>Same routing caveat as TC-002. Verified independently of the header/hero instances per TR-004.</t>
@@ -1066,13 +1082,17 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>1. Click the "FleetIQ" product mark (icon + wordmark) in the header
-   → The page scrolls back to the top (`#top`)</t>
+          <t>1. Inspect the header product mark's square icon
+   → The square icon contains the letter "F" beside the "FleetIQ" wordmark
+2. Click the "FleetIQ" product mark (icon + wordmark) in the header
+   → The page scrolls back to the top (`#top`)
+3. Scroll down again and click the same product mark a second time
+   → The page scrolls back to the top again — the behaviour is not limited to the first click</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>The page returns to its topmost scroll position</t>
+          <t>The mark renders as a square "F" icon beside the wordmark, and the page returns to its topmost scroll position every time the mark is clicked, not only on the first click</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
@@ -1087,13 +1107,17 @@
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N6" s="4" t="inlineStr"/>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>automation/tests/ui/test_landing.py::test_tc005_header_product_mark_scrolls_to_top</t>
+        </is>
+      </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>Distinct element and destination assertion from TC-006 (footer's "Back to top") even though both target `#top` -- role+name locators disambiguate them (plan.md B4)</t>
+          <t>Distinct element and destination assertion from TC-006 (footer's "Back to top") even though both target `#top` -- role+name locators disambiguate them (plan.md B4). Extended 2026-09-21 to exercise a second scroll-and-click cycle: TR-003 states the behaviour with no first-click-only qualifier, and a plain &lt;a href="#top"&gt; re-scrolls on every click in any browser (verified against a control page). Not a new requirement — coverage of text that was always there. Extended 2026-09-21 to assert the square icon contains "F": TR-003 states the mark is a square icon *containing "F"* beside the wordmark, and no case asserted the glyph. Coverage of existing text, not a new requirement.</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1162,14 @@
       <c r="I7" s="4" t="inlineStr">
         <is>
           <t>1. Click the "Back to top" link in the footer
-   → The page scrolls back to the top (`#top`)</t>
+   → The page scrolls back to the top (`#top`)
+2. Scroll down again and click "Back to top" a second time
+   → The page scrolls back to the top again — the behaviour is not limited to the first click</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>The page returns to its topmost scroll position</t>
+          <t>The page returns to its topmost scroll position every time the link is clicked, not only on the first click of a page load</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
@@ -1158,13 +1184,17 @@
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N7" s="4" t="inlineStr"/>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>automation/tests/ui/test_landing.py::test_tc006_footer_back_to_top_scrolls_to_top</t>
+        </is>
+      </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>Distinct element from TC-005 -- verified independently even though the destination is the same</t>
+          <t>Distinct element from TC-005 -- verified independently even though the destination is the same. Extended 2026-09-21 to exercise a second scroll-and-click cycle: TR-010 states the behaviour with no first-click-only qualifier, and a plain &lt;a href="#top"&gt; re-scrolls on every click in any browser (verified against a control page). Not a new requirement — coverage of text that was always there.</t>
         </is>
       </c>
     </row>
@@ -1231,10 +1261,14 @@
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N8" s="4" t="inlineStr"/>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>automation/tests/ui/test_landing.py::test_tc007_no_intercepting_modal_on_create_account</t>
+        </is>
+      </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
           <t>Negative flow. The design source's own modal copy ("This prototype covers the landing page only") confirms the modal must not exist in the real build</t>
@@ -1302,10 +1336,14 @@
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N9" s="4" t="inlineStr"/>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>automation/tests/ui/test_landing.py::test_tc008_footer_mark_is_non_interactive</t>
+        </is>
+      </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
           <t>Negative flow -- asserts absence of an `&lt;a&gt;`/interactive role on the footer mark</t>
@@ -1378,10 +1416,14 @@
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N10" s="4" t="inlineStr"/>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>automation/tests/ui/test_landing.py::test_tc009_authenticated_visitor_redirected_home</t>
+        </is>
+      </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
           <t>Skipped with an explicit reason if FLTIQ-35 is not yet deployed to the target environment (research.md R5) -- never a silent pass</t>
@@ -1453,10 +1495,14 @@
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N11" s="4" t="inlineStr"/>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>automation/tests/ui/test_landing.py::test_tc010_header_sign_in_navigates_to_signin</t>
+        </is>
+      </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
           <t>Added to match TR-004's existing three-location coverage -- the original Jira AC only enumerated locations for "Create account" (spec.md §11 finding)</t>
@@ -1528,10 +1574,14 @@
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N12" s="4" t="inlineStr"/>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>automation/tests/ui/test_landing.py::test_tc011_hero_sign_in_navigates_to_signin</t>
+        </is>
+      </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
           <t>Verified independently of the header instance per TR-005</t>
@@ -1603,10 +1653,14 @@
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N13" s="4" t="inlineStr"/>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>automation/tests/ui/test_landing.py::test_tc012_closing_sign_in_navigates_to_signin</t>
+        </is>
+      </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
           <t>Verified independently of the header/hero instances per TR-005</t>
@@ -1678,10 +1732,14 @@
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N14" s="4" t="inlineStr"/>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>automation/tests/ui/test_landing.py::test_tc014_hierarchy_default_selection_floor1</t>
+        </is>
+      </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
           <t>Also the EC-002 edge case from spec.md §5</t>
@@ -1755,10 +1813,14 @@
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N15" s="4" t="inlineStr"/>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>automation/tests/ui/test_landing.py::test_tc015_selecting_node_updates_detail_panel</t>
+        </is>
+      </c>
       <c r="O15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
@@ -1826,10 +1888,14 @@
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N16" s="4" t="inlineStr"/>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="N16" s="4" t="inlineStr">
+        <is>
+          <t>automation/tests/ui/test_landing.py::test_tc016_no_api_call_during_hierarchy_interaction</t>
+        </is>
+      </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
           <t>Asserts "no XHR/fetch at all" rather than filtering by host, per research.md R4 -- no `API_BASE_URL` is configured to filter against</t>
@@ -1906,10 +1972,14 @@
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N17" s="4" t="inlineStr"/>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>automation/tests/ui/test_landing.py::test_tc017_meta_distinct_from_devices</t>
+        </is>
+      </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
           <t>The specific regression case data-model.md flags -- for Floor 1/Floor 2/Unassigned the two fields happen to read alike, but must not be asserted as the same field generally</t>
@@ -1976,10 +2046,14 @@
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N18" s="4" t="inlineStr"/>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="N18" s="4" t="inlineStr">
+        <is>
+          <t>automation/tests/ui/test_landing.py::test_tc018_selected_row_visually_highlighted</t>
+        </is>
+      </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
           <t>Found via the §15a UI Element Enumeration retrofit (spec.md, 2026-09-19). Assert via `aria-pressed`, not exact CSS colour/box-shadow values, since the visual styling is design-system-owned (see plan.md B4/data-model.md)</t>
@@ -2046,10 +2120,14 @@
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N19" s="4" t="inlineStr"/>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>automation/tests/ui/test_landing.py::test_tc019_zero_device_boundary_node</t>
+        </is>
+      </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
           <t>Boundary case (data-model.md) and EC-006 from spec.md §5</t>
@@ -2124,10 +2202,14 @@
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N20" s="4" t="inlineStr"/>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>automation/tests/ui/test_landing.py::test_tc020_each_node_exact_note_text</t>
+        </is>
+      </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
           <t>Each note ties to a specific capability-card claim (data-model.md) -- this case confirms the demo backs up the marketing copy, not just arbitrary text</t>
@@ -2198,10 +2280,14 @@
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N21" s="4" t="inlineStr"/>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>automation/tests/ui/test_landing.py::test_tc021_largest_value_at_360px</t>
+        </is>
+      </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
           <t>Boundary case combining the largest data value (data-model.md) with the 360px viewport requirement (TR-011)</t>
@@ -2274,10 +2360,14 @@
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N22" s="4" t="inlineStr"/>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="N22" s="4" t="inlineStr">
+        <is>
+          <t>automation/tests/ui/test_landing.py::test_tc022_no_horizontal_scroll_at_360px</t>
+        </is>
+      </c>
       <c r="O22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
@@ -2345,10 +2435,14 @@
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N23" s="4" t="inlineStr"/>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t>automation/tests/ui/test_landing.py::test_tc023_keyboard_reachability_and_focus_indicator</t>
+        </is>
+      </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
           <t>Tab-order verification via Playwright's keyboard API directly (research.md R3) -- not delegated to axe</t>
@@ -2419,10 +2513,14 @@
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N24" s="4" t="inlineStr"/>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="N24" s="4" t="inlineStr">
+        <is>
+          <t>automation/tests/ui/test_landing.py::test_tc024_no_keyboard_trap</t>
+        </is>
+      </c>
       <c r="O24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
@@ -2489,10 +2587,14 @@
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N25" s="4" t="inlineStr"/>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="N25" s="4" t="inlineStr">
+        <is>
+          <t>automation/tests/ui/test_landing.py::test_tc025_contrast_meets_wcag_aa</t>
+        </is>
+      </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
           <t>Requires the new axe-core-based dependency pinned at /speckit-implement (plan.md B2)</t>
@@ -2563,10 +2665,14 @@
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N26" s="4" t="inlineStr"/>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="N26" s="4" t="inlineStr">
+        <is>
+          <t>automation/tests/ui/test_landing.py::test_tc026_usable_at_200_percent_zoom</t>
+        </is>
+      </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
           <t>Confirmed as a requirement by the requester on 2026-09-18 despite not being individually cited in FLTIQ-62's own AC field (spec.md §11)</t>
@@ -2640,10 +2746,14 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N27" s="4" t="inlineStr"/>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="N27" s="4" t="inlineStr">
+        <is>
+          <t>automation/tests/ui/test_landing.py::test_tc027_hierarchy_keyboard_operability</t>
+        </is>
+      </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
           <t>The design implements each node as a native `&lt;button&gt;`, a favourable implementation signal, not itself the requirement (spec.md Scenario 4 negative flow)</t>
@@ -2710,10 +2820,14 @@
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N28" s="4" t="inlineStr"/>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="N28" s="4" t="inlineStr">
+        <is>
+          <t>automation/tests/ui/test_landing.py::test_tc028_header_cta_order</t>
+        </is>
+      </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
           <t>Order is the opposite of the hero and closing section (TC-030, TC-033) -- verified per-section, never assumed consistent</t>
@@ -2786,10 +2900,14 @@
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N29" s="4" t="inlineStr"/>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="N29" s="4" t="inlineStr">
+        <is>
+          <t>automation/tests/ui/test_landing.py::test_tc029_hero_exact_copy</t>
+        </is>
+      </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
           <t>The "500+ devices" statistic's factual accuracy (not its presence) is a separate, elective, non-blocking question (spec.md §13b Q1)</t>
@@ -2856,10 +2974,14 @@
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N30" s="4" t="inlineStr"/>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="N30" s="4" t="inlineStr">
+        <is>
+          <t>automation/tests/ui/test_landing.py::test_tc030_hero_cta_order</t>
+        </is>
+      </c>
       <c r="O30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
@@ -2924,10 +3046,14 @@
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N31" s="4" t="inlineStr"/>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="N31" s="4" t="inlineStr">
+        <is>
+          <t>automation/tests/ui/test_landing.py::test_tc031_capabilities_exact_copy</t>
+        </is>
+      </c>
       <c r="O31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
@@ -2992,10 +3118,14 @@
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N32" s="4" t="inlineStr"/>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="N32" s="4" t="inlineStr">
+        <is>
+          <t>automation/tests/ui/test_landing.py::test_tc032_hierarchy_exact_copy</t>
+        </is>
+      </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
           <t>This heading/body was found during a requester screenshot cross-check, not on the first analysis pass (spec.md TR-019)</t>
@@ -3064,10 +3194,14 @@
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N33" s="4" t="inlineStr"/>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="N33" s="4" t="inlineStr">
+        <is>
+          <t>automation/tests/ui/test_landing.py::test_tc033_closing_exact_copy_and_order</t>
+        </is>
+      </c>
       <c r="O33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
@@ -3110,12 +3244,14 @@
       <c r="I34" s="4" t="inlineStr">
         <is>
           <t>1. Inspect the footer
-   → The "F" icon + "FleetIQ" wordmark, "©ACL Digital", and a "Back to top" link are all present</t>
+   → The "F" icon + "FleetIQ" wordmark, "©ACL Digital", and a "Back to top" link are all present
+2. Inspect the footer mark's square icon
+   → The square icon contains the letter "F", the same mark as the header</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>All three footer elements are present, structurally distinct from the header (TR-003)</t>
+          <t>All three footer elements are present, with the mark rendering the same square "F" icon as the header, structurally distinct from it (TR-003)</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
@@ -3130,13 +3266,17 @@
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N34" s="4" t="inlineStr"/>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="N34" s="4" t="inlineStr">
+        <is>
+          <t>automation/tests/ui/test_landing.py::test_tc034_footer_elements_present</t>
+        </is>
+      </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>Presence only -- behaviour of the mark (TC-008) and the link (TC-006) are covered separately</t>
+          <t>Presence only -- behaviour of the mark (TC-008) and the link (TC-006) are covered separately Extended 2026-09-21 to assert the square icon contains "F": TR-010 states the mark is a square icon *containing "F"* beside the wordmark, and no case asserted the glyph. Coverage of existing text, not a new requirement.</t>
         </is>
       </c>
     </row>
@@ -3281,10 +3421,14 @@
       </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N36" s="4" t="inlineStr"/>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="N36" s="4" t="inlineStr">
+        <is>
+          <t>automation/tests/ui/test_landing.py::test_tc036_no_overclaiming_capability</t>
+        </is>
+      </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
           <t>The "500+ devices" statistic's factual accuracy is a separate elective question (§13b Q1), not part of this literal-copy check</t>
@@ -3351,10 +3495,14 @@
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N37" s="4" t="inlineStr"/>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="N37" s="4" t="inlineStr">
+        <is>
+          <t>automation/tests/ui/test_landing.py::test_tc037_no_analytics_or_tracking</t>
+        </is>
+      </c>
       <c r="O37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
@@ -3417,10 +3565,14 @@
       </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N38" s="4" t="inlineStr"/>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="N38" s="4" t="inlineStr">
+        <is>
+          <t>automation/tests/ui/test_landing.py::test_tc038_no_out_of_scope_content</t>
+        </is>
+      </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
           <t>Deliberately excludes the hero's "Free while you set up your first fleet. No card required." line -- that line is tracked separately and exclusively under TR-018/TC-039, pending §13a Q1</t>
@@ -3487,10 +3639,14 @@
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N39" s="4" t="inlineStr"/>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="N39" s="4" t="inlineStr">
+        <is>
+          <t>automation/tests/ui/test_landing.py::test_tc039_hero_free_placeholder_line</t>
+        </is>
+      </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
           <t>Converted 2026-09-21 from a Blocked placeholder once CF-002 was resolved. TC-038 explicitly excludes this line from its own check -- it is asserted here only, not duplicated.</t>
@@ -3561,10 +3717,14 @@
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N40" s="4" t="inlineStr"/>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="N40" s="4" t="inlineStr">
+        <is>
+          <t>automation/tests/ui/test_landing.py::test_tc041_360px_combined_with_200_percent_zoom</t>
+        </is>
+      </c>
       <c r="O40" s="4" t="inlineStr">
         <is>
           <t>EC-005 from spec.md §5 -- a boundary combination of TR-011 and TR-014, not a new expected result</t>
@@ -3633,10 +3793,14 @@
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N41" s="4" t="inlineStr"/>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="N41" s="4" t="inlineStr">
+        <is>
+          <t>automation/tests/ui/test_landing.py::test_tc042_skeleton_loader_during_auth_resolution</t>
+        </is>
+      </c>
       <c r="O41" s="4" t="inlineStr">
         <is>
           <t>Converted 2026-09-21 from a Blocked placeholder once §13b Q2 was answered ("skeleton loader"), resolving EC-001 and creating TR-020 -- a wholly new requirement, not previously named by any source. Test-mechanics note: the real auth check likely resolves too quickly to observe naturally in a test run; intercept and delay the underlying request to make the window reliably observable, mirroring the network-interception technique already used for TR-008 (research.md R4).</t>
@@ -3769,10 +3933,14 @@
       </c>
       <c r="M43" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N43" s="4" t="inlineStr"/>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="N43" s="4" t="inlineStr">
+        <is>
+          <t>automation/tests/ui/test_landing.py::test_tc044_header_has_capabilities_and_hierarchy_anchors</t>
+        </is>
+      </c>
       <c r="O43" s="4" t="inlineStr">
         <is>
           <t>Presence only, per TR-003's own text -- the click-to-scroll behaviour these links produce is explicitly waived (EC-004, spec.md §5): guaranteed by the HTML anchor-link standard, not a distinct product requirement, and TC-040 (which tested that) was correctly removed on 2026-09-21. This case covers what a coverage review found genuinely missing: TR-003 requires these two links to exist, and no prior case asserted that they do.</t>
@@ -3841,10 +4009,14 @@
       </c>
       <c r="M44" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N44" s="4" t="inlineStr"/>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="N44" s="4" t="inlineStr">
+        <is>
+          <t>automation/tests/ui/test_landing.py::test_tc045_header_anchors_navigate_to_correct_section</t>
+        </is>
+      </c>
       <c r="O44" s="4" t="inlineStr">
         <is>
           <t>Distinct from EC-004's waiver (spec.md §5, narrowed 2026-09-21): EC-004 correctly waives testing that anchor-link scrolling works as a GENERIC browser mechanism. This case tests something browsers do not guarantee -- that this specific link is wired to this specific section's id, not swapped or mistyped -- verified against the design source's explicit href="#capabilities"/id="capabilities" and href="#hierarchy"/id="hierarchy" pairing, the same evidentiary basis TC-005 already uses for the product mark's href="#top". Found via a requester screenshot walkthrough, 2026-09-21.</t>
@@ -3863,7 +4035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4041,32 +4213,32 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Click the "FleetIQ" product mark (icon + wordmark) in the header</t>
+          <t>Inspect the header product mark's square icon</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>The page scrolls back to the top (`#top`)</t>
+          <t>The square icon contains the letter "F" beside the "FleetIQ" wordmark</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>TC-006</t>
+          <t>TC-005</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Footer "Back to top" link scrolls the page back to the top when clicked</t>
+          <t>Header product mark scrolls the page back to the top when clicked</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Click the "Back to top" link in the footer</t>
+          <t>Click the "FleetIQ" product mark (icon + wordmark) in the header</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -4078,87 +4250,87 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>TC-007</t>
+          <t>TC-005</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>No intercepting modal appears when "Create account" is clicked</t>
+          <t>Header product mark scrolls the page back to the top when clicked</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Click "Create account" in the header, hero, and closing section, one at a time</t>
+          <t>Scroll down again and click the same product mark a second time</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Navigation to the sign-up screen occurs each time</t>
+          <t>The page scrolls back to the top again — the behaviour is not limited to the first click</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>TC-007</t>
+          <t>TC-006</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>No intercepting modal appears when "Create account" is clicked</t>
+          <t>Footer "Back to top" link scrolls the page back to the top when clicked</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Inspect the page for any modal dialog appearing before navigation</t>
+          <t>Click the "Back to top" link in the footer</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>No modal dialog is shown at any point</t>
+          <t>The page scrolls back to the top (`#top`)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>TC-008</t>
+          <t>TC-006</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Footer FleetIQ mark is plain text and does not navigate when clicked</t>
+          <t>Footer "Back to top" link scrolls the page back to the top when clicked</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Attempt to click the "FleetIQ" mark (icon + wordmark) in the footer</t>
+          <t>Scroll down again and click "Back to top" a second time</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>No navigation, scroll, or focus change occurs -- the element is not a link</t>
+          <t>The page scrolls back to the top again — the behaviour is not limited to the first click</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>TC-009</t>
+          <t>TC-007</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Authenticated visitor is redirected to the home page; the landing page is not shown</t>
+          <t>No intercepting modal appears when "Create account" is clicked</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
@@ -4166,24 +4338,24 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>With an active session, navigate to the root URL</t>
+          <t>Click "Create account" in the header, hero, and closing section, one at a time</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>The browser is redirected to the visitor's home page</t>
+          <t>Navigation to the sign-up screen occurs each time</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>TC-009</t>
+          <t>TC-007</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Authenticated visitor is redirected to the home page; the landing page is not shown</t>
+          <t>No intercepting modal appears when "Create account" is clicked</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
@@ -4191,24 +4363,24 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Inspect the rendered page</t>
+          <t>Inspect the page for any modal dialog appearing before navigation</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>The public landing page content is never rendered, not even briefly</t>
+          <t>No modal dialog is shown at any point</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>TC-010</t>
+          <t>TC-008</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Header "Sign in" navigates to the sign-in screen</t>
+          <t>Footer FleetIQ mark is plain text and does not navigate when clicked</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
@@ -4216,24 +4388,24 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Click "Sign in" in the header</t>
+          <t>Attempt to click the "FleetIQ" mark (icon + wordmark) in the footer</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>The browser navigates to the sign-in screen (FLTIQ-35)</t>
+          <t>No navigation, scroll, or focus change occurs -- the element is not a link</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>TC-011</t>
+          <t>TC-009</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Hero "Sign in" navigates to the sign-in screen</t>
+          <t>Authenticated visitor is redirected to the home page; the landing page is not shown</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
@@ -4241,49 +4413,49 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Click "Sign in" in the hero section</t>
+          <t>With an active session, navigate to the root URL</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>The browser navigates to the sign-in screen (FLTIQ-35)</t>
+          <t>The browser is redirected to the visitor's home page</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>TC-012</t>
+          <t>TC-009</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Closing-section "Sign in" navigates to the sign-in screen</t>
+          <t>Authenticated visitor is redirected to the home page; the landing page is not shown</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Click "Sign in" in the closing section</t>
+          <t>Inspect the rendered page</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>The browser navigates to the sign-in screen (FLTIQ-35)</t>
+          <t>The public landing page content is never rendered, not even briefly</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>TC-014</t>
+          <t>TC-010</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Hierarchy explorer pre-selects "Floor 1" on first render</t>
+          <t>Header "Sign in" navigates to the sign-in screen</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
@@ -4291,24 +4463,24 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Load the landing page and locate the hierarchy explorer's detail panel</t>
+          <t>Click "Sign in" in the header</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>The detail panel shows "Floor 1"'s information (label, status, devices, type, source, note) with no visitor interaction</t>
+          <t>The browser navigates to the sign-in screen (FLTIQ-35)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>TC-015</t>
+          <t>TC-011</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Selecting a different node updates the detail panel without a full page reload</t>
+          <t>Hero "Sign in" navigates to the sign-in screen</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
@@ -4316,49 +4488,49 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Click a different node's row, e.g. "Floor 2"</t>
+          <t>Click "Sign in" in the hero section</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>The detail panel updates to Floor 2's label, status badge, device count, device type, config source and note</t>
+          <t>The browser navigates to the sign-in screen (FLTIQ-35)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>TC-015</t>
+          <t>TC-012</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Selecting a different node updates the detail panel without a full page reload</t>
+          <t>Closing-section "Sign in" navigates to the sign-in screen</t>
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Confirm no full page navigation/reload occurred</t>
+          <t>Click "Sign in" in the closing section</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>The page's navigation entry and header/footer remain unchanged; only the detail panel content changed</t>
+          <t>The browser navigates to the sign-in screen (FLTIQ-35)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>TC-016</t>
+          <t>TC-014</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>No FleetIQ API request fires while interacting with the hierarchy explorer</t>
+          <t>Hierarchy explorer pre-selects "Floor 1" on first render</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
@@ -4366,24 +4538,24 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Attach a request listener, then select a sequence of different nodes in the hierarchy explorer</t>
+          <t>Load the landing page and locate the hierarchy explorer's detail panel</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>No `xhr`/`fetch` request fires at any point during the interaction</t>
+          <t>The detail panel shows "Floor 1"'s information (label, status, devices, type, source, note) with no visitor interaction</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>TC-017</t>
+          <t>TC-015</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Building A and Building B tree rows show a subgroup count distinct from the detail panel's device count</t>
+          <t>Selecting a different node updates the detail panel without a full page reload</t>
         </is>
       </c>
       <c r="C21" s="4" t="n">
@@ -4391,24 +4563,24 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Inspect Building A's tree row (without selecting it)</t>
+          <t>Click a different node's row, e.g. "Floor 2"</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>The row's right-aligned text reads "2 subgroups"</t>
+          <t>The detail panel updates to Floor 2's label, status badge, device count, device type, config source and note</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>TC-017</t>
+          <t>TC-015</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Building A and Building B tree rows show a subgroup count distinct from the detail panel's device count</t>
+          <t>Selecting a different node updates the detail panel without a full page reload</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
@@ -4416,37 +4588,37 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Select Building A</t>
+          <t>Confirm no full page navigation/reload occurred</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>The detail panel's "Devices" field reads "79" -- a different value/meaning from the tree row's "2 subgroups"</t>
+          <t>The page's navigation entry and header/footer remain unchanged; only the detail panel content changed</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>TC-017</t>
+          <t>TC-016</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Building A and Building B tree rows show a subgroup count distinct from the detail panel's device count</t>
+          <t>No FleetIQ API request fires while interacting with the hierarchy explorer</t>
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Inspect Building B's tree row (without selecting it)</t>
+          <t>Attach a request listener, then select a sequence of different nodes in the hierarchy explorer</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>The row's right-aligned text reads "0 subgroups"</t>
+          <t>No `xhr`/`fetch` request fires at any point during the interaction</t>
         </is>
       </c>
     </row>
@@ -4462,141 +4634,141 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Select Building B</t>
+          <t>Inspect Building A's tree row (without selecting it)</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>The detail panel's "Devices" field reads "0"</t>
+          <t>The row's right-aligned text reads "2 subgroups"</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>TC-018</t>
+          <t>TC-017</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Selecting a node visually highlights that node's own tree row</t>
+          <t>Building A and Building B tree rows show a subgroup count distinct from the detail panel's device count</t>
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Select a node other than the default (e.g. "Floor 2")</t>
+          <t>Select Building A</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>That node's row shows `aria-pressed="true"` and a distinguishing background/left-edge style; the previously selected row no longer does</t>
+          <t>The detail panel's "Devices" field reads "79" -- a different value/meaning from the tree row's "2 subgroups"</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>TC-019</t>
+          <t>TC-017</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Selecting the zero-device node (Building B) updates the detail panel without error</t>
+          <t>Building A and Building B tree rows show a subgroup count distinct from the detail panel's device count</t>
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Select "Building B"</t>
+          <t>Inspect Building B's tree row (without selecting it)</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>The detail panel renders with Devices "0", Type "—", status "Empty", and its note text -- no blank fields, no console error</t>
+          <t>The row's right-aligned text reads "0 subgroups"</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>TC-020</t>
+          <t>TC-017</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Each of the five hierarchy nodes displays its own exact note text when selected</t>
+          <t>Building A and Building B tree rows show a subgroup count distinct from the detail panel's device count</t>
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Select "Building A"</t>
+          <t>Select Building B</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Note reads "Subgroups may override the organisation default. Two do."</t>
+          <t>The detail panel's "Devices" field reads "0"</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>TC-020</t>
+          <t>TC-018</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Each of the five hierarchy nodes displays its own exact note text when selected</t>
+          <t>Selecting a node visually highlights that node's own tree row</t>
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Select "Floor 1"</t>
+          <t>Select a node other than the default (e.g. "Floor 2")</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Note reads "A change applied here reaches 41 devices. Nothing is applied until you review the diff."</t>
+          <t>That node's row shows `aria-pressed="true"` and a distinguishing background/left-edge style; the previously selected row no longer does</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>TC-020</t>
+          <t>TC-019</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Each of the five hierarchy nodes displays its own exact note text when selected</t>
+          <t>Selecting the zero-device node (Building B) updates the detail panel without error</t>
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Select "Floor 2"</t>
+          <t>Select "Building B"</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Note reads "Three devices have not acknowledged the last push. They keep their previous configuration until they do."</t>
+          <t>The detail panel renders with Devices "0", Type "—", status "Empty", and its note text -- no blank fields, no console error</t>
         </is>
       </c>
     </row>
@@ -4612,16 +4784,16 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Select "Building B"</t>
+          <t>Select "Building A"</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Note reads "Devices appear here the moment they claim a provisioning token."</t>
+          <t>Note reads "Subgroups may override the organisation default. Two do."</t>
         </is>
       </c>
     </row>
@@ -4637,103 +4809,103 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Select "Unassigned"</t>
+          <t>Select "Floor 1"</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Note reads "Unassigned devices report telemetry but receive no configuration. Place them in a group to give them one."</t>
+          <t>Note reads "A change applied here reaches 41 devices. Nothing is applied until you review the diff."</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>TC-021</t>
+          <t>TC-020</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Selecting "Unassigned" (501 devices, the largest fixture value) renders without truncation at 360px</t>
+          <t>Each of the five hierarchy nodes displays its own exact note text when selected</t>
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Select the "Unassigned" node</t>
+          <t>Select "Floor 2"</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>The detail panel renders "501" in the Devices field with no truncation, overflow, or horizontal scroll introduced</t>
+          <t>Note reads "Three devices have not acknowledged the last push. They keep their previous configuration until they do."</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>TC-022</t>
+          <t>TC-020</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Page renders with no horizontal scroll or truncation at a 360px viewport</t>
+          <t>Each of the five hierarchy nodes displays its own exact note text when selected</t>
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Load the landing page at 360px width</t>
+          <t>Select "Building B"</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>No horizontal scrollbar appears</t>
+          <t>Note reads "Devices appear here the moment they claim a provisioning token."</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>TC-022</t>
+          <t>TC-020</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Page renders with no horizontal scroll or truncation at a 360px viewport</t>
+          <t>Each of the five hierarchy nodes displays its own exact note text when selected</t>
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Inspect every section (header, hero, capabilities, hierarchy, closing, footer)</t>
+          <t>Select "Unassigned"</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>No content is truncated or overlapping</t>
+          <t>Note reads "Unassigned devices report telemetry but receive no configuration. Place them in a group to give them one."</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>TC-023</t>
+          <t>TC-021</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Every link, section anchor, and hierarchy-explorer node is reachable and operable via keyboard with a visible focus indicator</t>
+          <t>Selecting "Unassigned" (501 devices, the largest fixture value) renders without truncation at 360px</t>
         </is>
       </c>
       <c r="C35" s="4" t="n">
@@ -4741,24 +4913,24 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Press Tab repeatedly from the top of the page</t>
+          <t>Select the "Unassigned" node</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Focus moves through the header links, hero CTAs, capability cards (if focusable), hierarchy nodes, closing CTAs, and footer links, each showing a visible focus indicator</t>
+          <t>The detail panel renders "501" in the Devices field with no truncation, overflow, or horizontal scroll introduced</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>TC-024</t>
+          <t>TC-022</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>No keyboard trap exists anywhere on the page</t>
+          <t>Page renders with no horizontal scroll or truncation at a 360px viewport</t>
         </is>
       </c>
       <c r="C36" s="4" t="n">
@@ -4766,49 +4938,49 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Tab forward through every focusable element to the end of the page, then Shift+Tab back to the start</t>
+          <t>Load the landing page at 360px width</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Focus always advances/retreats; it never becomes stuck on one element</t>
+          <t>No horizontal scrollbar appears</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>TC-025</t>
+          <t>TC-022</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Text and control-boundary contrast meets WCAG 2.1 AA thresholds</t>
+          <t>Page renders with no horizontal scroll or truncation at a 360px viewport</t>
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Run the axe-core-based contrast scan (research.md R3) across the full page</t>
+          <t>Inspect every section (header, hero, capabilities, hierarchy, closing, footer)</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Normal text measures at least 4.5:1; large text and control boundaries measure at least 3:1</t>
+          <t>No content is truncated or overlapping</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>TC-026</t>
+          <t>TC-023</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Page remains usable at 200% browser zoom with no content or function lost</t>
+          <t>Every link, section anchor, and hierarchy-explorer node is reachable and operable via keyboard with a visible focus indicator</t>
         </is>
       </c>
       <c r="C38" s="4" t="n">
@@ -4816,24 +4988,24 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Load the landing page at the halved viewport</t>
+          <t>Press Tab repeatedly from the top of the page</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>All content and functionality (CTAs, hierarchy explorer, nav anchors) remain visible and operable</t>
+          <t>Focus moves through the header links, hero CTAs, capability cards (if focusable), hierarchy nodes, closing CTAs, and footer links, each showing a visible focus indicator</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>TC-027</t>
+          <t>TC-024</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Hierarchy explorer nodes are selectable via keyboard with the same visible focus indicator as the rest of the page</t>
+          <t>No keyboard trap exists anywhere on the page</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
@@ -4841,49 +5013,49 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Tab to a hierarchy-explorer node</t>
+          <t>Tab forward through every focusable element to the end of the page, then Shift+Tab back to the start</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>The node shows the same visible focus indicator as any other control</t>
+          <t>Focus always advances/retreats; it never becomes stuck on one element</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>TC-027</t>
+          <t>TC-025</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Hierarchy explorer nodes are selectable via keyboard with the same visible focus indicator as the rest of the page</t>
+          <t>Text and control-boundary contrast meets WCAG 2.1 AA thresholds</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Press Enter or Space</t>
+          <t>Run the axe-core-based contrast scan (research.md R3) across the full page</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>The node becomes selected and the detail panel updates, identical to a mouse click</t>
+          <t>Normal text measures at least 4.5:1; large text and control boundaries measure at least 3:1</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>TC-028</t>
+          <t>TC-026</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Header displays "Sign in" before "Create account"</t>
+          <t>Page remains usable at 200% browser zoom with no content or function lost</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
@@ -4891,24 +5063,24 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Inspect the header's control group</t>
+          <t>Load the landing page at the halved viewport</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>"Sign in" appears before "Create account" in DOM/visual order</t>
+          <t>All content and functionality (CTAs, hierarchy explorer, nav anchors) remain visible and operable</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>TC-029</t>
+          <t>TC-027</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Hero renders the exact badge, headline, subhead, and three supporting statistics</t>
+          <t>Hierarchy explorer nodes are selectable via keyboard with the same visible focus indicator as the rest of the page</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
@@ -4916,24 +5088,24 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Inspect the hero badge</t>
+          <t>Tab to a hierarchy-explorer node</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Reads exactly "Multi-tenant device management"</t>
+          <t>The node shows the same visible focus indicator as any other control</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>TC-029</t>
+          <t>TC-027</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Hero renders the exact badge, headline, subhead, and three supporting statistics</t>
+          <t>Hierarchy explorer nodes are selectable via keyboard with the same visible focus indicator as the rest of the page</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
@@ -4941,37 +5113,37 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Inspect the headline</t>
+          <t>Press Enter or Space</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Reads exactly "Every device in your fleet, in one hierarchy."</t>
+          <t>The node becomes selected and the detail panel updates, identical to a mouse click</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>TC-029</t>
+          <t>TC-028</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Hero renders the exact badge, headline, subhead, and three supporting statistics</t>
+          <t>Header displays "Sign in" before "Create account"</t>
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Inspect the subhead</t>
+          <t>Inspect the header's control group</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Reads exactly "One place to define device types, organise thousands of units into groups, and review a configuration change before it lands."</t>
+          <t>"Sign in" appears before "Create account" in DOM/visual order</t>
         </is>
       </c>
     </row>
@@ -4987,103 +5159,103 @@
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Inspect the three statistics</t>
+          <t>Inspect the hero badge</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Read exactly "500+ devices onboarded in a single import", "3 levels of grouping, enforced by the platform", "4 roles, from tenant owner to read-only viewer"</t>
+          <t>Reads exactly "Multi-tenant device management"</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>TC-030</t>
+          <t>TC-029</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Hero displays "Create account" before "Sign in"</t>
+          <t>Hero renders the exact badge, headline, subhead, and three supporting statistics</t>
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Inspect the hero's CTA group</t>
+          <t>Inspect the headline</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>"Create account" appears before "Sign in" in DOM/visual order</t>
+          <t>Reads exactly "Every device in your fleet, in one hierarchy."</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>TC-031</t>
+          <t>TC-029</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Capabilities section renders the exact heading and all six capability cards' copy</t>
+          <t>Hero renders the exact badge, headline, subhead, and three supporting statistics</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Inspect the section heading</t>
+          <t>Inspect the subhead</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Reads exactly "Built for fleets that outgrew the spreadsheet."</t>
+          <t>Reads exactly "One place to define device types, organise thousands of units into groups, and review a configuration change before it lands."</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>TC-031</t>
+          <t>TC-029</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Capabilities section renders the exact heading and all six capability cards' copy</t>
+          <t>Hero renders the exact badge, headline, subhead, and three supporting statistics</t>
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Inspect all six capability cards in order (01-06)</t>
+          <t>Inspect the three statistics</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Each card's title and body match spec.md TR-007 verbatim, in the numbered order 01 through 06</t>
+          <t>Read exactly "500+ devices onboarded in a single import", "3 levels of grouping, enforced by the platform", "4 roles, from tenant owner to read-only viewer"</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>TC-032</t>
+          <t>TC-030</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Hierarchy section renders the exact heading and intro paragraph</t>
+          <t>Hero displays "Create account" before "Sign in"</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
@@ -5091,124 +5263,124 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Inspect the hierarchy section's heading</t>
+          <t>Inspect the hero's CTA group</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Reads exactly "Group once. Configure the group."</t>
+          <t>"Create account" appears before "Sign in" in DOM/visual order</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>TC-032</t>
+          <t>TC-031</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Hierarchy section renders the exact heading and intro paragraph</t>
+          <t>Capabilities section renders the exact heading and all six capability cards' copy</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Inspect the intro paragraph</t>
+          <t>Inspect the section heading</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>Reads exactly "Devices inherit configuration from the group they sit in, so a change to a floor reaches forty units without touching one of them individually. Unassigned devices stay visible until someone places them."</t>
+          <t>Reads exactly "Built for fleets that outgrew the spreadsheet."</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>TC-033</t>
+          <t>TC-031</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Closing section displays "Create account" before "Sign in"</t>
+          <t>Capabilities section renders the exact heading and all six capability cards' copy</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Inspect the closing section's heading and body</t>
+          <t>Inspect all six capability cards in order (01-06)</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>Heading reads exactly "Set up your organisation in three steps."; body reads exactly "Sign up, verify your email, name your organisation. You will be adding device types the same afternoon."</t>
+          <t>Each card's title and body match spec.md TR-007 verbatim, in the numbered order 01 through 06</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>TC-033</t>
+          <t>TC-032</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Closing section displays "Create account" before "Sign in"</t>
+          <t>Hierarchy section renders the exact heading and intro paragraph</t>
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Inspect the closing section's CTA group</t>
+          <t>Inspect the hierarchy section's heading</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>"Create account" appears before "Sign in", the same order as the hero and opposite the header</t>
+          <t>Reads exactly "Group once. Configure the group."</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>TC-034</t>
+          <t>TC-032</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Footer displays the FleetIQ mark, "©ACL Digital" attribution, and "Back to top" link</t>
+          <t>Hierarchy section renders the exact heading and intro paragraph</t>
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Inspect the footer</t>
+          <t>Inspect the intro paragraph</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>The "F" icon + "FleetIQ" wordmark, "©ACL Digital", and a "Back to top" link are all present</t>
+          <t>Reads exactly "Devices inherit configuration from the group they sit in, so a change to a floor reaches forty units without touching one of them individually. Unassigned devices stay visible until someone places them."</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>TC-035</t>
+          <t>TC-033</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Every visual element resolves to a shared design-system token or component</t>
+          <t>Closing section displays "Create account" before "Sign in"</t>
         </is>
       </c>
       <c r="C54" s="4" t="n">
@@ -5216,24 +5388,24 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Perform a component-usage/token audit against the Keel design system (spec.md §11's proposed resolution)</t>
+          <t>Inspect the closing section's heading and body</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>No page-specific styling (inline colour/spacing literals) is found</t>
+          <t>Heading reads exactly "Set up your organisation in three steps."; body reads exactly "Sign up, verify your email, name your organisation. You will be adding device types the same afternoon."</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>TC-035</t>
+          <t>TC-033</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Every visual element resolves to a shared design-system token or component</t>
+          <t>Closing section displays "Create account" before "Sign in"</t>
         </is>
       </c>
       <c r="C55" s="4" t="n">
@@ -5241,24 +5413,24 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Compare the rendered page against the approved design in a manual visual-regression review (plan.md A3)</t>
+          <t>Inspect the closing section's CTA group</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Visual fidelity matches the design system's tokens and components</t>
+          <t>"Create account" appears before "Sign in", the same order as the hero and opposite the header</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>TC-036</t>
+          <t>TC-034</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Page copy makes no capability claim exceeding what MVP1 supports</t>
+          <t>Footer displays the FleetIQ mark, "©ACL Digital" attribution, and "Back to top" link</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
@@ -5266,49 +5438,49 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Compare every capability claim on the page against the checklist (three levels of grouping, four roles, diff-based review, viewer-timezone audit, tenant isolation as a boundary)</t>
+          <t>Inspect the footer</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>No claim on the page exceeds what is on the checklist</t>
+          <t>The "F" icon + "FleetIQ" wordmark, "©ACL Digital", and a "Back to top" link are all present</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>TC-037</t>
+          <t>TC-034</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>No analytics or tracking request is observed during page load or interaction</t>
+          <t>Footer displays the FleetIQ mark, "©ACL Digital" attribution, and "Back to top" link</t>
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Load the page and interact with every CTA and the hierarchy explorer while monitoring outbound network activity</t>
+          <t>Inspect the footer mark's square icon</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>No request to a known analytics/tracking endpoint pattern is observed</t>
+          <t>The square icon contains the letter "F", the same mark as the header</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>TC-038</t>
+          <t>TC-035</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>No pricing, documentation, blog, contact-form, or demo-request content is present</t>
+          <t>Every visual element resolves to a shared design-system token or component</t>
         </is>
       </c>
       <c r="C58" s="4" t="n">
@@ -5316,49 +5488,49 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Inspect the full page for pricing tables, documentation links, a blog section, a contact form, or demo-request content</t>
+          <t>Perform a component-usage/token audit against the Keel design system (spec.md §11's proposed resolution)</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>None of these elements are present anywhere on the page</t>
+          <t>No page-specific styling (inline colour/spacing literals) is found</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>TC-039</t>
+          <t>TC-035</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Hero displays "Free while you set up your first fleet. No card required." beneath the calls to action</t>
+          <t>Every visual element resolves to a shared design-system token or component</t>
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Inspect the hero section beneath the calls to action</t>
+          <t>Compare the rendered page against the approved design in a manual visual-regression review (plan.md A3)</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>The line "Free while you set up your first fleet. No card required." is present, exactly as designed</t>
+          <t>Visual fidelity matches the design system's tokens and components</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>TC-041</t>
+          <t>TC-036</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Page remains usable with no content loss at 360px combined with 200% zoom</t>
+          <t>Page copy makes no capability claim exceeding what MVP1 supports</t>
         </is>
       </c>
       <c r="C60" s="4" t="n">
@@ -5366,24 +5538,24 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Load the landing page at the combined boundary viewport</t>
+          <t>Compare every capability claim on the page against the checklist (three levels of grouping, four roles, diff-based review, viewer-timezone audit, tenant isolation as a boundary)</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>No horizontal scroll is introduced beyond what 360px alone requires, and no content or function is lost</t>
+          <t>No claim on the page exceeds what is on the checklist</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>TC-042</t>
+          <t>TC-037</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Skeleton loader displays while auth state resolves at first paint</t>
+          <t>No analytics or tracking request is observed during page load or interaction</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
@@ -5391,49 +5563,49 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Navigate to the root URL with the auth-check request delayed</t>
+          <t>Load the page and interact with every CTA and the hierarchy explorer while monitoring outbound network activity</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>A skeleton loader is visible immediately, before either the landing page or an authenticated redirect renders</t>
+          <t>No request to a known analytics/tracking endpoint pattern is observed</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>TC-042</t>
+          <t>TC-038</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Skeleton loader displays while auth state resolves at first paint</t>
+          <t>No pricing, documentation, blog, contact-form, or demo-request content is present</t>
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Allow the delayed auth-check to resolve</t>
+          <t>Inspect the full page for pricing tables, documentation links, a blog section, a contact form, or demo-request content</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>The skeleton loader is replaced by the correct outcome -- the landing page (TR-001) for an unauthenticated visitor, or the home-page redirect (TR-002) for an authenticated one</t>
+          <t>None of these elements are present anywhere on the page</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>TC-043</t>
+          <t>TC-039</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>[BLOCKED] Hierarchy explorer behaviour if its client-side script fails to load</t>
+          <t>Hero displays "Free while you set up your first fleet. No card required." beneath the calls to action</t>
         </is>
       </c>
       <c r="C63" s="4" t="n">
@@ -5441,24 +5613,24 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Do not execute this case until spec.md §13b Q3 is answered and EC-003 states a fallback behaviour</t>
+          <t>Inspect the hero section beneath the calls to action</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>N/A -- placeholder only, no assertion is made</t>
+          <t>The line "Free while you set up your first fleet. No card required." is present, exactly as designed</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>TC-044</t>
+          <t>TC-041</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Header displays "Capabilities" and "Hierarchy" as section-anchor links</t>
+          <t>Page remains usable with no content loss at 360px combined with 200% zoom</t>
         </is>
       </c>
       <c r="C64" s="4" t="n">
@@ -5466,24 +5638,24 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Inspect the header's nav area, between the product mark and the Sign in/Create account controls</t>
+          <t>Load the landing page at the combined boundary viewport</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>"Capabilities" and "Hierarchy" both render as clickable links (`&lt;a&gt;` elements), not plain text</t>
+          <t>No horizontal scroll is introduced beyond what 360px alone requires, and no content or function is lost</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>TC-045</t>
+          <t>TC-042</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Header "Capabilities" and "Hierarchy" links each navigate to their own correct, distinct section</t>
+          <t>Skeleton loader displays while auth state resolves at first paint</t>
         </is>
       </c>
       <c r="C65" s="4" t="n">
@@ -5491,24 +5663,24 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Click "Capabilities" in the header</t>
+          <t>Navigate to the root URL with the auth-check request delayed</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>The page scrolls to the Capabilities section -- confirmed by the heading "Built for fleets that outgrew the spreadsheet." (TR-007) becoming visible, not the Hierarchy section</t>
+          <t>A skeleton loader is visible immediately, before either the landing page or an authenticated redirect renders</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>TC-045</t>
+          <t>TC-042</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Header "Capabilities" and "Hierarchy" links each navigate to their own correct, distinct section</t>
+          <t>Skeleton loader displays while auth state resolves at first paint</t>
         </is>
       </c>
       <c r="C66" s="4" t="n">
@@ -5516,10 +5688,110 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
+          <t>Allow the delayed auth-check to resolve</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>The skeleton loader is replaced by the correct outcome -- the landing page (TR-001) for an unauthenticated visitor, or the home-page redirect (TR-002) for an authenticated one</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>TC-043</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>[BLOCKED] Hierarchy explorer behaviour if its client-side script fails to load</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>Do not execute this case until spec.md §13b Q3 is answered and EC-003 states a fallback behaviour</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>N/A -- placeholder only, no assertion is made</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>TC-044</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>Header displays "Capabilities" and "Hierarchy" as section-anchor links</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>Inspect the header's nav area, between the product mark and the Sign in/Create account controls</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>"Capabilities" and "Hierarchy" both render as clickable links (`&lt;a&gt;` elements), not plain text</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>TC-045</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>Header "Capabilities" and "Hierarchy" links each navigate to their own correct, distinct section</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>Click "Capabilities" in the header</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>The page scrolls to the Capabilities section -- confirmed by the heading "Built for fleets that outgrew the spreadsheet." (TR-007) becoming visible, not the Hierarchy section</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>TC-045</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>Header "Capabilities" and "Hierarchy" links each navigate to their own correct, distinct section</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
           <t>From the top of the page, click "Hierarchy" in the header</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr">
+      <c r="E70" s="4" t="inlineStr">
         <is>
           <t>The page scrolls to the Hierarchy section -- confirmed by the heading "Group once. Configure the group." (TR-019) becoming visible, not the Capabilities section</t>
         </is>
@@ -5616,7 +5888,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
     </row>
@@ -5641,7 +5913,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
     </row>
@@ -5662,7 +5934,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>4/4</t>
         </is>
       </c>
     </row>
@@ -5687,7 +5959,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>4/4</t>
         </is>
       </c>
     </row>
@@ -5712,7 +5984,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>3/3</t>
         </is>
       </c>
     </row>
@@ -5733,7 +6005,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/2</t>
         </is>
       </c>
     </row>
@@ -5754,7 +6026,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
     </row>
@@ -5779,7 +6051,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>0/8</t>
+          <t>8/8</t>
         </is>
       </c>
     </row>
@@ -5800,7 +6072,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
     </row>
@@ -5821,7 +6093,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>3/3</t>
         </is>
       </c>
     </row>
@@ -5846,7 +6118,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>3/3</t>
         </is>
       </c>
     </row>
@@ -5871,7 +6143,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>3/3</t>
         </is>
       </c>
     </row>
@@ -5896,7 +6168,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
     </row>
@@ -5921,7 +6193,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/2</t>
         </is>
       </c>
     </row>
@@ -5971,7 +6243,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
     </row>
@@ -5992,7 +6264,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/2</t>
         </is>
       </c>
     </row>
@@ -6013,7 +6285,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6306,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
     </row>
@@ -6055,7 +6327,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
     </row>

--- a/specs/001-fltiq-62-public-landing-page/test-cases.xlsx
+++ b/specs/001-fltiq-62-public-landing-page/test-cases.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-21T20:45:00</t>
+          <t>2026-09-22T02:15:00</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>The specific regression case data-model.md flags -- for Floor 1/Floor 2/Unassigned the two fields happen to read alike, but must not be asserted as the same field generally</t>
+          <t>The specific regression case data-model.md flags -- for Floor 1/Floor 2/Unassigned the two fields happen to read alike, but must not be asserted as the same field generally Hardened 2026-09-22 (constitution VII.a): assertion changed from a substring check against the whole tree row's concatenated text to an exact `==` comparison against the isolated meta span's own text, so a wrong or partially-correct value can no longer pass. Coverage of existing requirement text, not a new requirement.</t>
         </is>
       </c>
     </row>
@@ -2800,12 +2800,12 @@
       <c r="I28" s="4" t="inlineStr">
         <is>
           <t>1. Inspect the header's control group
-   → "Sign in" appears before "Create account" in DOM/visual order</t>
+   → The controls read exactly "Sign in" then "Create account", in that order</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>The header's CTA order matches the design source exactly</t>
+          <t>The header's CTA labels and their order match the design source exactly, case included</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>Order is the opposite of the hero and closing section (TC-030, TC-033) -- verified per-section, never assumed consistent</t>
+          <t>Order is the opposite of the hero and closing section (TC-030, TC-033) -- verified per-section, never assumed consistent Strengthened 2026-09-21: the CTA check now compares the labels exactly and in order (case-sensitive) instead of matching a lowercased substring, after a design cross-check found the build ships "Create an account" where the design says "Create account". Coverage of TR-003's existing text, not a new requirement.</t>
         </is>
       </c>
     </row>
@@ -2954,12 +2954,12 @@
       <c r="I30" s="4" t="inlineStr">
         <is>
           <t>1. Inspect the hero's CTA group
-   → "Create account" appears before "Sign in" in DOM/visual order</t>
+   → The CTAs read exactly "Create account" then "Sign in", in that order</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>The hero's CTA order matches the design source exactly -- the reverse of the header</t>
+          <t>The hero's CTA labels and their order match the design source exactly -- the reverse order of the header</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
@@ -2982,7 +2982,11 @@
           <t>automation/tests/ui/test_landing.py::test_tc030_hero_cta_order</t>
         </is>
       </c>
-      <c r="O30" s="4" t="inlineStr"/>
+      <c r="O30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Strengthened 2026-09-21: the CTA check now compares the labels exactly and in order (case-sensitive) instead of matching a lowercased substring, after a design cross-check found the build ships "Create an account" where the design says "Create account". Coverage of TR-006's existing text, not a new requirement.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -3074,7 +3078,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>TR-019</t>
+          <t>TR-019, TR-008</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr"/>
@@ -3098,12 +3102,14 @@
           <t>1. Inspect the hierarchy section's heading
    → Reads exactly "Group once. Configure the group."
 2. Inspect the intro paragraph
-   → Reads exactly "Devices inherit configuration from the group they sit in, so a change to a floor reaches forty units without touching one of them individually. Unassigned devices stay visible until someone places them."</t>
+   → Reads exactly "Devices inherit configuration from the group they sit in, so a change to a floor reaches forty units without touching one of them individually. Unassigned devices stay visible until someone places them."
+3. Inspect the hierarchy panel's own header line, above the node rows
+   → Reads exactly "XYZ — organisation"</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>The hierarchy section's heading and intro copy match the approved design verbatim</t>
+          <t>The hierarchy section's heading and intro copy match the approved design verbatim, and the tree panel's own header line reads "XYZ — organisation" exactly</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
@@ -3128,7 +3134,7 @@
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>This heading/body was found during a requester screenshot cross-check, not on the first analysis pass (spec.md TR-019)</t>
+          <t>This heading/body was found during a requester screenshot cross-check, not on the first analysis pass (spec.md TR-019) Extended 2026-09-22 to add the panel header line (TR-008), after a requester screenshot comparison caught that spec.md's own §13b Q4 closure (2026-09-21) had never been acted on for this element -- it was still untested and mis-cited in §11 as an open question a full day after closing. See D10 in reports/test-report-cycle-1.md and data-model.md's new field entry.</t>
         </is>
       </c>
     </row>
@@ -3174,12 +3180,12 @@
           <t>1. Inspect the closing section's heading and body
    → Heading reads exactly "Set up your organisation in three steps."; body reads exactly "Sign up, verify your email, name your organisation. You will be adding device types the same afternoon."
 2. Inspect the closing section's CTA group
-   → "Create account" appears before "Sign in", the same order as the hero and opposite the header</t>
+   → The CTAs read exactly "Create account" then "Sign in", the same order as the hero and opposite the header</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>The closing section's copy and CTA order match the approved design verbatim</t>
+          <t>The closing section's copy and CTA labels/order match the design source exactly</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
@@ -3202,7 +3208,11 @@
           <t>automation/tests/ui/test_landing.py::test_tc033_closing_exact_copy_and_order</t>
         </is>
       </c>
-      <c r="O33" s="4" t="inlineStr"/>
+      <c r="O33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Strengthened 2026-09-21: the CTA check now compares the labels exactly and in order (case-sensitive) instead of matching a lowercased substring, after a design cross-check found the build ships "Create an account" where the design says "Create account". Coverage of TR-009's existing text, not a new requirement.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -3276,7 +3286,7 @@
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>Presence only -- behaviour of the mark (TC-008) and the link (TC-006) are covered separately Extended 2026-09-21 to assert the square icon contains "F": TR-010 states the mark is a square icon *containing "F"* beside the wordmark, and no case asserted the glyph. Coverage of existing text, not a new requirement.</t>
+          <t>Presence only -- behaviour of the mark (TC-008) and the link (TC-006) are covered separately Extended 2026-09-21 to assert the square icon contains "F": TR-010 states the mark is a square icon *containing "F"* beside the wordmark, and no case asserted the glyph. Coverage of existing text, not a new requirement. Hardened 2026-09-22 (constitution VII.a): assertion changed from a substring check against the whole footer's concatenated text to an exact `==` comparison against the isolated mark/attribution element's own text, so a wrong or partially-correct value can no longer pass. Coverage of existing requirement text, not a new requirement.</t>
         </is>
       </c>
     </row>
@@ -3323,15 +3333,17 @@
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>1. Perform a component-usage/token audit against the Keel design system (spec.md §11's proposed resolution)
-   → No page-specific styling (inline colour/spacing literals) is found
-2. Compare the rendered page against the approved design in a manual visual-regression review (plan.md A3)
+          <t>1. Compare each surface's rendered background against the Keel token the design source declares for it (body, header, stats section, capabilities grid, capability card, hierarchy panel, closing section, footer)
+   → Every surface resolves to its declared token: --keel-bg #F7F8FA for the page, --keel-surface #FFFFFF for header/stats/cards/panel/footer, --keel-deck-navy #000D35 for the closing section, and no background on the capabilities grid
+2. Check that capability cards and the hierarchy panel carry a 1px --keel-border border, --keel-radius-lg radius and --keel-shadow-sm shadow, and that the header carries a bottom border
+   → All present
+3. Compare the rendered page against the approved design in a manual visual-regression review (plan.md A3)
    → Visual fidelity matches the design system's tokens and components</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>The page is built entirely on shared design-system tokens/components, with no page-specific styling</t>
+          <t>The page is built entirely on shared design-system tokens/components, with each token applied to the property the design declares it for, and no page-specific styling</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
@@ -3341,18 +3353,22 @@
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="N35" s="4" t="inlineStr"/>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="N35" s="4" t="inlineStr">
+        <is>
+          <t>automation/tests/ui/test_landing.py::test_tc035_design_system_token_application</t>
+        </is>
+      </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>Not independently machine-verifiable via a single Playwright assertion (spec.md §11); a partial automated token/component audit supplements the manual visual-regression review (plan.md A3)</t>
+          <t>Partially automated 2026-09-21 (task T038): the token-application audit is a deterministic computed-style comparison against the tokens the design source declares, so it is automatable after all -- the earlier `automatable: false` treated a bookkeeping flag as a technical limit and left visual verification with no executed coverage at all. A requester screenshot comparison found the capabilities grid rendering --keel-border as a background. The manual visual-regression half (pixel fidelity, spacing, typography rendering) remains manual per plan.md A3. All checks are collected and reported together because these defects cluster.</t>
         </is>
       </c>
     </row>
@@ -4035,7 +4051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E70"/>
+  <dimension ref="A1:E72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5143,7 +5159,7 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>"Sign in" appears before "Create account" in DOM/visual order</t>
+          <t>The controls read exactly "Sign in" then "Create account", in that order</t>
         </is>
       </c>
     </row>
@@ -5268,7 +5284,7 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>"Create account" appears before "Sign in" in DOM/visual order</t>
+          <t>The CTAs read exactly "Create account" then "Sign in", in that order</t>
         </is>
       </c>
     </row>
@@ -5375,25 +5391,25 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>TC-033</t>
+          <t>TC-032</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Closing section displays "Create account" before "Sign in"</t>
+          <t>Hierarchy section renders the exact heading and intro paragraph</t>
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Inspect the closing section's heading and body</t>
+          <t>Inspect the hierarchy panel's own header line, above the node rows</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>Heading reads exactly "Set up your organisation in three steps."; body reads exactly "Sign up, verify your email, name your organisation. You will be adding device types the same afternoon."</t>
+          <t>Reads exactly "XYZ — organisation"</t>
         </is>
       </c>
     </row>
@@ -5409,41 +5425,41 @@
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Inspect the closing section's CTA group</t>
+          <t>Inspect the closing section's heading and body</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>"Create account" appears before "Sign in", the same order as the hero and opposite the header</t>
+          <t>Heading reads exactly "Set up your organisation in three steps."; body reads exactly "Sign up, verify your email, name your organisation. You will be adding device types the same afternoon."</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>TC-034</t>
+          <t>TC-033</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Footer displays the FleetIQ mark, "©ACL Digital" attribution, and "Back to top" link</t>
+          <t>Closing section displays "Create account" before "Sign in"</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Inspect the footer</t>
+          <t>Inspect the closing section's CTA group</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>The "F" icon + "FleetIQ" wordmark, "©ACL Digital", and a "Back to top" link are all present</t>
+          <t>The CTAs read exactly "Create account" then "Sign in", the same order as the hero and opposite the header</t>
         </is>
       </c>
     </row>
@@ -5459,41 +5475,41 @@
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Inspect the footer mark's square icon</t>
+          <t>Inspect the footer</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>The square icon contains the letter "F", the same mark as the header</t>
+          <t>The "F" icon + "FleetIQ" wordmark, "©ACL Digital", and a "Back to top" link are all present</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>TC-035</t>
+          <t>TC-034</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Every visual element resolves to a shared design-system token or component</t>
+          <t>Footer displays the FleetIQ mark, "©ACL Digital" attribution, and "Back to top" link</t>
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Perform a component-usage/token audit against the Keel design system (spec.md §11's proposed resolution)</t>
+          <t>Inspect the footer mark's square icon</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>No page-specific styling (inline colour/spacing literals) is found</t>
+          <t>The square icon contains the letter "F", the same mark as the header</t>
         </is>
       </c>
     </row>
@@ -5509,78 +5525,78 @@
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Compare the rendered page against the approved design in a manual visual-regression review (plan.md A3)</t>
+          <t>Compare each surface's rendered background against the Keel token the design source declares for it (body, header, stats section, capabilities grid, capability card, hierarchy panel, closing section, footer)</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>Visual fidelity matches the design system's tokens and components</t>
+          <t>Every surface resolves to its declared token: --keel-bg #F7F8FA for the page, --keel-surface #FFFFFF for header/stats/cards/panel/footer, --keel-deck-navy #000D35 for the closing section, and no background on the capabilities grid</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>TC-036</t>
+          <t>TC-035</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Page copy makes no capability claim exceeding what MVP1 supports</t>
+          <t>Every visual element resolves to a shared design-system token or component</t>
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Compare every capability claim on the page against the checklist (three levels of grouping, four roles, diff-based review, viewer-timezone audit, tenant isolation as a boundary)</t>
+          <t>Check that capability cards and the hierarchy panel carry a 1px --keel-border border, --keel-radius-lg radius and --keel-shadow-sm shadow, and that the header carries a bottom border</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>No claim on the page exceeds what is on the checklist</t>
+          <t>All present</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>TC-037</t>
+          <t>TC-035</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>No analytics or tracking request is observed during page load or interaction</t>
+          <t>Every visual element resolves to a shared design-system token or component</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Load the page and interact with every CTA and the hierarchy explorer while monitoring outbound network activity</t>
+          <t>Compare the rendered page against the approved design in a manual visual-regression review (plan.md A3)</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>No request to a known analytics/tracking endpoint pattern is observed</t>
+          <t>Visual fidelity matches the design system's tokens and components</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>TC-038</t>
+          <t>TC-036</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>No pricing, documentation, blog, contact-form, or demo-request content is present</t>
+          <t>Page copy makes no capability claim exceeding what MVP1 supports</t>
         </is>
       </c>
       <c r="C62" s="4" t="n">
@@ -5588,24 +5604,24 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Inspect the full page for pricing tables, documentation links, a blog section, a contact form, or demo-request content</t>
+          <t>Compare every capability claim on the page against the checklist (three levels of grouping, four roles, diff-based review, viewer-timezone audit, tenant isolation as a boundary)</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>None of these elements are present anywhere on the page</t>
+          <t>No claim on the page exceeds what is on the checklist</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>TC-039</t>
+          <t>TC-037</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Hero displays "Free while you set up your first fleet. No card required." beneath the calls to action</t>
+          <t>No analytics or tracking request is observed during page load or interaction</t>
         </is>
       </c>
       <c r="C63" s="4" t="n">
@@ -5613,24 +5629,24 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Inspect the hero section beneath the calls to action</t>
+          <t>Load the page and interact with every CTA and the hierarchy explorer while monitoring outbound network activity</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>The line "Free while you set up your first fleet. No card required." is present, exactly as designed</t>
+          <t>No request to a known analytics/tracking endpoint pattern is observed</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>TC-041</t>
+          <t>TC-038</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Page remains usable with no content loss at 360px combined with 200% zoom</t>
+          <t>No pricing, documentation, blog, contact-form, or demo-request content is present</t>
         </is>
       </c>
       <c r="C64" s="4" t="n">
@@ -5638,24 +5654,24 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Load the landing page at the combined boundary viewport</t>
+          <t>Inspect the full page for pricing tables, documentation links, a blog section, a contact form, or demo-request content</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>No horizontal scroll is introduced beyond what 360px alone requires, and no content or function is lost</t>
+          <t>None of these elements are present anywhere on the page</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>TC-042</t>
+          <t>TC-039</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Skeleton loader displays while auth state resolves at first paint</t>
+          <t>Hero displays "Free while you set up your first fleet. No card required." beneath the calls to action</t>
         </is>
       </c>
       <c r="C65" s="4" t="n">
@@ -5663,49 +5679,49 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Navigate to the root URL with the auth-check request delayed</t>
+          <t>Inspect the hero section beneath the calls to action</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>A skeleton loader is visible immediately, before either the landing page or an authenticated redirect renders</t>
+          <t>The line "Free while you set up your first fleet. No card required." is present, exactly as designed</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>TC-042</t>
+          <t>TC-041</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Skeleton loader displays while auth state resolves at first paint</t>
+          <t>Page remains usable with no content loss at 360px combined with 200% zoom</t>
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Allow the delayed auth-check to resolve</t>
+          <t>Load the landing page at the combined boundary viewport</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>The skeleton loader is replaced by the correct outcome -- the landing page (TR-001) for an unauthenticated visitor, or the home-page redirect (TR-002) for an authenticated one</t>
+          <t>No horizontal scroll is introduced beyond what 360px alone requires, and no content or function is lost</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>TC-043</t>
+          <t>TC-042</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>[BLOCKED] Hierarchy explorer behaviour if its client-side script fails to load</t>
+          <t>Skeleton loader displays while auth state resolves at first paint</t>
         </is>
       </c>
       <c r="C67" s="4" t="n">
@@ -5713,49 +5729,49 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Do not execute this case until spec.md §13b Q3 is answered and EC-003 states a fallback behaviour</t>
+          <t>Navigate to the root URL with the auth-check request delayed</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>N/A -- placeholder only, no assertion is made</t>
+          <t>A skeleton loader is visible immediately, before either the landing page or an authenticated redirect renders</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>TC-044</t>
+          <t>TC-042</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Header displays "Capabilities" and "Hierarchy" as section-anchor links</t>
+          <t>Skeleton loader displays while auth state resolves at first paint</t>
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Inspect the header's nav area, between the product mark and the Sign in/Create account controls</t>
+          <t>Allow the delayed auth-check to resolve</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>"Capabilities" and "Hierarchy" both render as clickable links (`&lt;a&gt;` elements), not plain text</t>
+          <t>The skeleton loader is replaced by the correct outcome -- the landing page (TR-001) for an unauthenticated visitor, or the home-page redirect (TR-002) for an authenticated one</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>TC-045</t>
+          <t>TC-043</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Header "Capabilities" and "Hierarchy" links each navigate to their own correct, distinct section</t>
+          <t>[BLOCKED] Hierarchy explorer behaviour if its client-side script fails to load</t>
         </is>
       </c>
       <c r="C69" s="4" t="n">
@@ -5763,35 +5779,85 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Click "Capabilities" in the header</t>
+          <t>Do not execute this case until spec.md §13b Q3 is answered and EC-003 states a fallback behaviour</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>The page scrolls to the Capabilities section -- confirmed by the heading "Built for fleets that outgrew the spreadsheet." (TR-007) becoming visible, not the Hierarchy section</t>
+          <t>N/A -- placeholder only, no assertion is made</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
+          <t>TC-044</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>Header displays "Capabilities" and "Hierarchy" as section-anchor links</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>Inspect the header's nav area, between the product mark and the Sign in/Create account controls</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>"Capabilities" and "Hierarchy" both render as clickable links (`&lt;a&gt;` elements), not plain text</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
           <t>TC-045</t>
         </is>
       </c>
-      <c r="B70" s="4" t="inlineStr">
+      <c r="B71" s="4" t="inlineStr">
         <is>
           <t>Header "Capabilities" and "Hierarchy" links each navigate to their own correct, distinct section</t>
         </is>
       </c>
-      <c r="C70" s="4" t="n">
+      <c r="C71" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>Click "Capabilities" in the header</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>The page scrolls to the Capabilities section -- confirmed by the heading "Built for fleets that outgrew the spreadsheet." (TR-007) becoming visible, not the Hierarchy section</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>TC-045</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>Header "Capabilities" and "Hierarchy" links each navigate to their own correct, distinct section</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D70" s="4" t="inlineStr">
+      <c r="D72" s="4" t="inlineStr">
         <is>
           <t>From the top of the page, click "Hierarchy" in the header</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
+      <c r="E72" s="4" t="inlineStr">
         <is>
           <t>The page scrolls to the Hierarchy section -- confirmed by the heading "Group once. Configure the group." (TR-019) becoming visible, not the Capabilities section</t>
         </is>
@@ -6043,15 +6109,15 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>TC-014, TC-015, TC-016, TC-017, TC-018, TC-019, TC-020, TC-021</t>
+          <t>TC-014, TC-015, TC-016, TC-017, TC-018, TC-019, TC-020, TC-021, TC-032</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>8/8</t>
+          <t>9/9</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6284,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
     </row>
